--- a/data/merged/2026-09-28/MERGED_JP_Robot-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_JP_Robot-Vacuum_2026-09-28.xlsx
@@ -7578,94 +7578,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7991,7 +7903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -18767,210 +18679,35 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0H3SZKNG5</t>
-        </is>
-      </c>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
+          <t>B0FD3Q3HDQ</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>颜色: 2-黑色</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>品牌: Lefant | 型号名称: M310 mop | 推荐表面: 地板 | 特殊功能: 4500Pa 3档吸力调整→500毫升垃圾桶→从陀螺仪到点激光测距进化→一体化机身结构→180分钟→最适合单人生活的最佳→擦拭擦拭→附带遥控器(支架另售) | 颜色: 黑色</t>
+        </is>
+      </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>roborock</t>
+          <t>Lefant</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/Roborock/page/5E4CAAB4-2101-4304-A4F8-E09C730688AE?lp_asin=B0H3SZKNG5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/Lefant/page/9C72F38B-D744-433C-984D-924C2CF60DBF?lp_asin=B0FD3Q3HDQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>【购买套装】roborock Qrevo Edge 2 机器人吸尘器 &amp; 正规消耗品垃圾收集用纸袋 (3张) 套装</t>
+          <t>Lefant M310 扫地机器人 无刷吸口 不缠绕 自动充电 多种清洁模式 4500Pa强力吸力 180分钟连续工作</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>套装内容:Qrevo Edge 2 机器人吸尘器、垃圾收集用纸袋(3张)
-垃圾收集纸袋：请定期更换自动收集的垃圾纸袋，以防止其装满。如果纸袋积累过多，可能会影响自动收集功能。</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H3SZKNG5?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/310n8Y3Io5L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>B0H3SZKNG5</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O44" s="13">
-        <v>46623</v>
-      </c>
-      <c r="P44" s="13">
-        <v>-24416</v>
-      </c>
-      <c r="Q44" s="14">
-        <v>-0.64</v>
-      </c>
-      <c r="R44" s="15" t="inlineStr">
-        <is>
-          <t>机器人 (家居、厨具、家装)</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="T44" s="13">
-        <v>24</v>
-      </c>
-      <c r="U44" s="14"/>
-      <c r="V44" s="13">
-        <v>2277168</v>
-      </c>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="13">
-        <v>94882</v>
-      </c>
-      <c r="AA44" s="2"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="17"/>
-      <c r="AE44" s="13"/>
-      <c r="AF44" s="18"/>
-      <c r="AG44" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="13"/>
-      <c r="AI44" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AL44" s="17">
-        <v>116</v>
-      </c>
-      <c r="AM44" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN44" s="11"/>
-      <c r="AO44" s="11"/>
-      <c r="AP44" s="2"/>
-      <c r="AQ44" s="17">
-        <v>4</v>
-      </c>
-      <c r="AR44" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS44" s="12" t="inlineStr">
-        <is>
-          <t>Roborock JP</t>
-        </is>
-      </c>
-      <c r="AT44" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU44" s="11" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV44" s="12" t="inlineStr">
-        <is>
-          <t>KWUN TONG 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW44" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJLV5TPJIYO7G</t>
-        </is>
-      </c>
-      <c r="AX44" s="11"/>
-      <c r="AY44" s="11"/>
-      <c r="AZ44" s="11"/>
-      <c r="BA44" s="11"/>
-      <c r="BB44" s="11"/>
-      <c r="BC44" s="11"/>
-      <c r="BD44" s="11"/>
-      <c r="BE44" s="11"/>
-      <c r="BF44" s="11"/>
-      <c r="BG44" s="11"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="20"/>
-      <c r="BJ44" s="20"/>
-      <c r="BK44" s="20"/>
-      <c r="BL44" s="20"/>
-      <c r="BM44" s="20"/>
-      <c r="BN44" s="20"/>
-      <c r="BO44" s="20"/>
-      <c r="BP44" s="20"/>
-      <c r="BQ44" s="20"/>
-      <c r="BR44" s="11"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B0FD3Q3HDQ</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>颜色: 2-黑色</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Lefant | 型号名称: M310 mop | 推荐表面: 地板 | 特殊功能: 4500Pa 3档吸力调整→500毫升垃圾桶→从陀螺仪到点激光测距进化→一体化机身结构→180分钟→最适合单人生活的最佳→擦拭擦拭→附带遥控器(支架另售) | 颜色: 黑色</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Lefant</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Lefant/page/9C72F38B-D744-433C-984D-924C2CF60DBF?lp_asin=B0FD3Q3HDQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>Lefant M310 扫地机器人 无刷吸口 不缠绕 自动充电 多种清洁模式 4500Pa强力吸力 180分钟连续工作</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>M210P 升级版 - 陀螺仪进化为重点激光测距! 精确度提升了障碍物检测。 夜间家具识别也强化,高速响应,减少碰撞风险。 可智能应对复杂的环境。
 M310清扫机器人实现了M210P的2.5倍的吸力! 采用无刷吸嘴,消除头发缠绕。 无需再打扫。
@@ -18980,19 +18717,259 @@
 包装内容:Lefant M310、充电站、AC适配器、侧刷、使用说明书</t>
         </is>
       </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0FD3Q3HDQ?psc=1</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41a1mhAFYmL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>B0H94R793P</t>
+        </is>
+      </c>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
+        </is>
+      </c>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O44" s="13">
+        <v>27376</v>
+      </c>
+      <c r="P44" s="13">
+        <v>-12344</v>
+      </c>
+      <c r="Q44" s="14">
+        <v>-0.82</v>
+      </c>
+      <c r="R44" s="15" t="inlineStr">
+        <is>
+          <t>机器人 (家居、厨具、家装)</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="T44" s="13">
+        <v>113</v>
+      </c>
+      <c r="U44" s="14">
+        <v>1.1</v>
+      </c>
+      <c r="V44" s="13">
+        <v>2259887</v>
+      </c>
+      <c r="W44" s="13"/>
+      <c r="X44" s="13"/>
+      <c r="Y44" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z44" s="13">
+        <v>19999</v>
+      </c>
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="17">
+        <v>2985</v>
+      </c>
+      <c r="AE44" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="18">
+        <v>4.2</v>
+      </c>
+      <c r="AG44" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="13">
+        <v>532</v>
+      </c>
+      <c r="AI44" s="14">
+        <v>0.82</v>
+      </c>
+      <c r="AJ44"/>
+      <c r="AK44" s="11" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AL44" s="17">
+        <v>433</v>
+      </c>
+      <c r="AM44" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN44" s="11"/>
+      <c r="AO44" s="11"/>
+      <c r="AP44" s="2"/>
+      <c r="AQ44" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR44" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS44" s="12" t="inlineStr">
+        <is>
+          <t>Clean Robot Hong Kong Technology Co.,Limited</t>
+        </is>
+      </c>
+      <c r="AT44" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU44" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV44" s="12" t="inlineStr">
+        <is>
+          <t>HONG KONG HONG KONG 999077 CN</t>
+        </is>
+      </c>
+      <c r="AW44" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MNLSSQJOAPSN</t>
+        </is>
+      </c>
+      <c r="AX44" s="11"/>
+      <c r="AY44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ44" s="11"/>
+      <c r="BA44" s="11"/>
+      <c r="BB44" s="11"/>
+      <c r="BC44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE44" s="11"/>
+      <c r="BF44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG44" s="11"/>
+      <c r="BH44" s="12"/>
+      <c r="BI44" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
+      <c r="BJ44" s="20" t="inlineStr">
+        <is>
+          <t>3.3 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK44" s="20" t="inlineStr">
+        <is>
+          <t>3.30 kg</t>
+        </is>
+      </c>
+      <c r="BL44" s="20" t="inlineStr">
+        <is>
+          <t>28長さ x 28幅 x 7.9高さ cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="20"/>
+      <c r="BN44" s="20" t="inlineStr">
+        <is>
+          <t>3.3 kg</t>
+        </is>
+      </c>
+      <c r="BO44" s="20" t="inlineStr">
+        <is>
+          <t>3.30 kg</t>
+        </is>
+      </c>
+      <c r="BP44" s="20" t="inlineStr">
+        <is>
+          <t>38.6 x 34.3 x 11.4 cm</t>
+        </is>
+      </c>
+      <c r="BQ44" s="20" t="inlineStr">
+        <is>
+          <t>38.60 x 34.30 x 11.40 cm</t>
+        </is>
+      </c>
+      <c r="BR44" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>B0FSKG1CGR</t>
+        </is>
+      </c>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>品牌: HOBOT | 颜色: 白色 | 商品尺寸: 29.5长度 x 14.8宽度 x 9.5高度 厘米 | 电池组成: 锂离子电池 | 是否随附电池: 否</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>HOBOT</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/HOBOT/page/5FD3BD3C-4B59-4EF0-998B-639025A0DFC5?lp_asin=B0FSKG1CGR&amp;ref_=ast_bln</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>HOBOT-R3 LIXIL原装套装 [全自动清洁窗户] Hobot 窗户机器人 窗户清洁 搭载AI功能 日语客户支持 玻璃 水擦拭 干擦 窗户 自动清洁 窗户用 节省空间设计 防掉落 机器人吸尘器 玻璃清洁剂 喷雾 喷绘 强力吸力</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>窗户清洁机器人</t>
+        </is>
+      </c>
       <c r="J45" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0FD3Q3HDQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0FSKG1CGR?psc=1</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41a1mhAFYmL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/319+CshNDML._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>B0H94R793P</t>
+          <t>B0FSKG1CGR</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
@@ -19006,13 +18983,13 @@
         </is>
       </c>
       <c r="O45" s="13">
-        <v>27376</v>
+        <v>34486</v>
       </c>
       <c r="P45" s="13">
-        <v>-12344</v>
+        <v>31771</v>
       </c>
       <c r="Q45" s="14">
-        <v>-0.82</v>
+        <v>0.56</v>
       </c>
       <c r="R45" s="15" t="inlineStr">
         <is>
@@ -19021,55 +18998,59 @@
       </c>
       <c r="S45" s="16" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T45" s="13">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="U45" s="14">
-        <v>1.1</v>
+        <v>0.28</v>
       </c>
       <c r="V45" s="13">
-        <v>2259887</v>
-      </c>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
+        <v>2062500</v>
+      </c>
+      <c r="W45" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X45" s="13">
+        <v>2062500</v>
+      </c>
       <c r="Y45" s="17">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z45" s="13">
-        <v>19999</v>
+        <v>41250</v>
       </c>
       <c r="AA45" s="2"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="17">
-        <v>2985</v>
+        <v>20</v>
       </c>
       <c r="AE45" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF45" s="18">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AG45" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="13">
-        <v>532</v>
-      </c>
+        <v>0.02</v>
+      </c>
+      <c r="AH45" s="13"/>
       <c r="AI45" s="14">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="11" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="AL45" s="17">
-        <v>433</v>
+        <v>349</v>
       </c>
       <c r="AM45" s="11" t="inlineStr">
         <is>
@@ -19080,14 +19061,14 @@
       <c r="AO45" s="11"/>
       <c r="AP45" s="2"/>
       <c r="AQ45" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR45" s="17">
         <v>1</v>
       </c>
       <c r="AS45" s="12" t="inlineStr">
         <is>
-          <t>Clean Robot Hong Kong Technology Co.,Limited</t>
+          <t>HOBOT Japan アマゾン店</t>
         </is>
       </c>
       <c r="AT45" s="11" t="inlineStr">
@@ -19097,25 +19078,21 @@
       </c>
       <c r="AU45" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV45" s="12" t="inlineStr">
         <is>
-          <t>HONG KONG HONG KONG 999077 CN</t>
+          <t>品川区 東京都 1410033 JP</t>
         </is>
       </c>
       <c r="AW45" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MNLSSQJOAPSN</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHEZ9DMV8Q508</t>
         </is>
       </c>
       <c r="AX45" s="11"/>
-      <c r="AY45" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY45" s="11"/>
       <c r="AZ45" s="11"/>
       <c r="BA45" s="11"/>
       <c r="BB45" s="11"/>
@@ -19137,52 +19114,20 @@
       </c>
       <c r="BG45" s="11"/>
       <c r="BH45" s="12"/>
-      <c r="BI45" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
-      <c r="BJ45" s="20" t="inlineStr">
-        <is>
-          <t>3.3 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK45" s="20" t="inlineStr">
-        <is>
-          <t>3.30 kg</t>
-        </is>
-      </c>
+      <c r="BI45" s="20"/>
+      <c r="BJ45" s="20"/>
+      <c r="BK45" s="20"/>
       <c r="BL45" s="20" t="inlineStr">
         <is>
-          <t>28長さ x 28幅 x 7.9高さ cm</t>
+          <t>29.5長さ x 14.8幅 x 9.5高さ cm</t>
         </is>
       </c>
       <c r="BM45" s="20"/>
-      <c r="BN45" s="20" t="inlineStr">
-        <is>
-          <t>3.3 kg</t>
-        </is>
-      </c>
-      <c r="BO45" s="20" t="inlineStr">
-        <is>
-          <t>3.30 kg</t>
-        </is>
-      </c>
-      <c r="BP45" s="20" t="inlineStr">
-        <is>
-          <t>38.6 x 34.3 x 11.4 cm</t>
-        </is>
-      </c>
-      <c r="BQ45" s="20" t="inlineStr">
-        <is>
-          <t>38.60 x 34.30 x 11.40 cm</t>
-        </is>
-      </c>
-      <c r="BR45" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+      <c r="BN45" s="20"/>
+      <c r="BO45" s="20"/>
+      <c r="BP45" s="20"/>
+      <c r="BQ45" s="20"/>
+      <c r="BR45" s="11"/>
     </row>
     <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11">
@@ -19191,243 +19136,35 @@
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>B0FSKG1CGR</t>
-        </is>
-      </c>
-      <c r="D46" s="12"/>
+          <t>B0F4CKCQSR</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>样式: L6 Aqua</t>
+        </is>
+      </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>品牌: HOBOT | 颜色: 白色 | 商品尺寸: 29.5长度 x 14.8宽度 x 9.5高度 厘米 | 电池组成: 锂离子电池 | 是否随附电池: 否</t>
+          <t>品牌: OKP Life | 型号名称: L6 Aqua | 推荐表面: 地毯 | 特殊功能: 预约计时器 | 颜色: 白色</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>HOBOT</t>
+          <t>OKP Life</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/HOBOT/page/5FD3BD3C-4B59-4EF0-998B-639025A0DFC5?lp_asin=B0FSKG1CGR&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/OKPLIFE/page/23AA7D3D-6376-403F-8AD6-A176BA24E310?lp_asin=B0F4CKCQSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>HOBOT-R3 LIXIL原装套装 [全自动清洁窗户] Hobot 窗户机器人 窗户清洁 搭载AI功能 日语客户支持 玻璃 水擦拭 干擦 窗户 自动清洁 窗户用 节省空间设计 防掉落 机器人吸尘器 玻璃清洁剂 喷雾 喷绘 强力吸力</t>
+          <t>OKP Life 机器人吸尘器 L6 Aqua [2合1吸尘和水拖双用清洁机器人/LiDAR导航/9.5厘米超小型/6000Pa 强力吸尘/静音设计 远程操作 自动充电 防跌落/2.4G和5G Wi-Fi 兼容/Alexa Google Home 兼容] 白色</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>窗户清洁机器人</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0FSKG1CGR?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/319+CshNDML._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>B0FSKG1CGR</t>
-        </is>
-      </c>
-      <c r="M46" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
-        </is>
-      </c>
-      <c r="N46" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O46" s="13">
-        <v>34486</v>
-      </c>
-      <c r="P46" s="13">
-        <v>31771</v>
-      </c>
-      <c r="Q46" s="14">
-        <v>0.56</v>
-      </c>
-      <c r="R46" s="15" t="inlineStr">
-        <is>
-          <t>机器人 (家居、厨具、家装)</t>
-        </is>
-      </c>
-      <c r="S46" s="16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="T46" s="13">
-        <v>50</v>
-      </c>
-      <c r="U46" s="14">
-        <v>0.28</v>
-      </c>
-      <c r="V46" s="13">
-        <v>2062500</v>
-      </c>
-      <c r="W46" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X46" s="13">
-        <v>2062500</v>
-      </c>
-      <c r="Y46" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="13">
-        <v>41250</v>
-      </c>
-      <c r="AA46" s="2"/>
-      <c r="AB46" s="1"/>
-      <c r="AC46" s="2"/>
-      <c r="AD46" s="17">
-        <v>20</v>
-      </c>
-      <c r="AE46" s="13">
-        <v>1</v>
-      </c>
-      <c r="AF46" s="18">
-        <v>3.7</v>
-      </c>
-      <c r="AG46" s="19">
-        <v>0.02</v>
-      </c>
-      <c r="AH46" s="13"/>
-      <c r="AI46" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="11" t="inlineStr">
-        <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="AL46" s="17">
-        <v>349</v>
-      </c>
-      <c r="AM46" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN46" s="11"/>
-      <c r="AO46" s="11"/>
-      <c r="AP46" s="2"/>
-      <c r="AQ46" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR46" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS46" s="12" t="inlineStr">
-        <is>
-          <t>HOBOT Japan アマゾン店</t>
-        </is>
-      </c>
-      <c r="AT46" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU46" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV46" s="12" t="inlineStr">
-        <is>
-          <t>品川区 東京都 1410033 JP</t>
-        </is>
-      </c>
-      <c r="AW46" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHEZ9DMV8Q508</t>
-        </is>
-      </c>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD46" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE46" s="11"/>
-      <c r="BF46" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG46" s="11"/>
-      <c r="BH46" s="12"/>
-      <c r="BI46" s="20"/>
-      <c r="BJ46" s="20"/>
-      <c r="BK46" s="20"/>
-      <c r="BL46" s="20" t="inlineStr">
-        <is>
-          <t>29.5長さ x 14.8幅 x 9.5高さ cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="20"/>
-      <c r="BN46" s="20"/>
-      <c r="BO46" s="20"/>
-      <c r="BP46" s="20"/>
-      <c r="BQ46" s="20"/>
-      <c r="BR46" s="11"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11">
-        <v>46</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12" t="inlineStr">
-        <is>
-          <t>B0F4CKCQSR</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>样式: L6 Aqua</t>
-        </is>
-      </c>
-      <c r="E47" s="12" t="inlineStr">
-        <is>
-          <t>品牌: OKP Life | 型号名称: L6 Aqua | 推荐表面: 地毯 | 特殊功能: 预约计时器 | 颜色: 白色</t>
-        </is>
-      </c>
-      <c r="F47" s="12" t="inlineStr">
-        <is>
-          <t>OKP Life</t>
-        </is>
-      </c>
-      <c r="G47" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/OKPLIFE/page/23AA7D3D-6376-403F-8AD6-A176BA24E310?lp_asin=B0F4CKCQSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H47" s="12" t="inlineStr">
-        <is>
-          <t>OKP Life 机器人吸尘器 L6 Aqua [2合1吸尘和水拖双用清洁机器人/LiDAR导航/9.5厘米超小型/6000Pa 强力吸尘/静音设计 远程操作 自动充电 防跌落/2.4G和5G Wi-Fi 兼容/Alexa Google Home 兼容] 白色</t>
-        </is>
-      </c>
-      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>【6000Pa的强力吸力】L6 Aqua扫地机器人实现最高6000Pa的吸力。 通过安静高效的动作，可以简单地去除隐藏在缝隙和地毯中的灰尘和宠物毛。 此外,还搭载了智能传感器,根据地板材质自动调节吸力,在彻底清洁的同时不会伤害地板。
 【高精度地图】OKP LIFE L6 Aqua 通过先进的LiDAR DToF 技术扫描房间,产生高精度的地图,优化清洁路线。 支持最多3层楼的地图，通过应用程序自由设置路线和禁止进入区域，定制每个楼层的清洁计划。
@@ -19438,418 +19175,240 @@
 【多种清扫模式和自动充电功能】这款机器人配备了4种清扫模式：之字形、随机、局部、边缘。 这些灵活的清洁模式确保彻底清洁，适应各种需求和环境。 当电池剩余量低于15%时，机器人会自动返回充电底座。 当电池电量达到80%时，它会返回停止位置，重新开始清扫，并不会反复清扫。</t>
         </is>
       </c>
-      <c r="J47" s="12" t="inlineStr">
+      <c r="J46" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B0F4CKCQSR?psc=1</t>
         </is>
       </c>
-      <c r="K47" s="12" t="inlineStr">
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/71NLEOxrsQL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L47" s="12" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>B0GDFJ5R1P</t>
         </is>
       </c>
-      <c r="M47" s="12" t="inlineStr">
+      <c r="M46" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
         </is>
       </c>
-      <c r="N47" s="12" t="inlineStr">
+      <c r="N46" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装</t>
         </is>
       </c>
-      <c r="O47" s="13">
+      <c r="O46" s="13">
         <v>46153</v>
       </c>
-      <c r="P47" s="13">
+      <c r="P46" s="13">
         <v>-103135</v>
       </c>
-      <c r="Q47" s="14">
+      <c r="Q46" s="14">
         <v>-3.86</v>
       </c>
-      <c r="R47" s="15" t="inlineStr">
+      <c r="R46" s="15" t="inlineStr">
         <is>
           <t>机器人 (家居、厨具、家装)</t>
         </is>
       </c>
-      <c r="S47" s="16" t="inlineStr">
+      <c r="S46" s="16" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="T47" s="13">
+      <c r="T46" s="13">
         <v>70</v>
       </c>
-      <c r="U47" s="14">
+      <c r="U46" s="14">
         <v>-0.33</v>
       </c>
-      <c r="V47" s="13">
+      <c r="V46" s="13">
         <v>1608600</v>
       </c>
-      <c r="W47" s="13" t="inlineStr">
+      <c r="W46" s="13" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="X47" s="13">
+      <c r="X46" s="13">
         <v>948914</v>
       </c>
-      <c r="Y47" s="17">
+      <c r="Y46" s="17">
         <v>1</v>
       </c>
-      <c r="Z47" s="13">
+      <c r="Z46" s="13">
         <v>22980</v>
       </c>
-      <c r="AA47" s="2"/>
-      <c r="AB47" s="1"/>
-      <c r="AC47" s="2"/>
-      <c r="AD47" s="17">
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="17">
         <v>18</v>
       </c>
-      <c r="AE47" s="13">
+      <c r="AE46" s="13">
         <v>2</v>
       </c>
-      <c r="AF47" s="18">
+      <c r="AF46" s="18">
         <v>3.8</v>
       </c>
-      <c r="AG47" s="19">
+      <c r="AG46" s="19">
         <v>0.0286</v>
       </c>
-      <c r="AH47" s="13">
+      <c r="AH46" s="13">
         <v>532</v>
       </c>
-      <c r="AI47" s="14">
+      <c r="AI46" s="14">
         <v>0.83</v>
       </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="11" t="inlineStr">
+      <c r="AJ46"/>
+      <c r="AK46" s="11" t="inlineStr">
         <is>
           <t>2025-07-04</t>
         </is>
       </c>
-      <c r="AL47" s="17">
+      <c r="AL46" s="17">
         <v>451</v>
       </c>
-      <c r="AM47" s="11" t="inlineStr">
+      <c r="AM46" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN47" s="11"/>
-      <c r="AO47" s="11"/>
-      <c r="AP47" s="2"/>
-      <c r="AQ47" s="17">
+      <c r="AN46" s="11"/>
+      <c r="AO46" s="11"/>
+      <c r="AP46" s="2"/>
+      <c r="AQ46" s="17">
         <v>10</v>
       </c>
-      <c r="AR47" s="17">
+      <c r="AR46" s="17">
         <v>1</v>
       </c>
-      <c r="AS47" s="12" t="inlineStr">
+      <c r="AS46" s="12" t="inlineStr">
         <is>
           <t>OKP Life Tech</t>
         </is>
       </c>
-      <c r="AT47" s="11" t="inlineStr">
+      <c r="AT46" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU47" s="11" t="inlineStr">
+      <c r="AU46" s="11" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="AV47" s="12" t="inlineStr">
+      <c r="AV46" s="12" t="inlineStr">
         <is>
           <t>深圳市 广东省 516473 CN</t>
         </is>
       </c>
-      <c r="AW47" s="11" t="inlineStr">
+      <c r="AW46" s="11" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A95AMKZGJE5P0</t>
         </is>
       </c>
-      <c r="AX47" s="11"/>
-      <c r="AY47" s="11"/>
-      <c r="AZ47" s="11"/>
-      <c r="BA47" s="11"/>
-      <c r="BB47" s="11"/>
-      <c r="BC47" s="11" t="inlineStr">
+      <c r="AX46" s="11"/>
+      <c r="AY46" s="11"/>
+      <c r="AZ46" s="11"/>
+      <c r="BA46" s="11"/>
+      <c r="BB46" s="11"/>
+      <c r="BC46" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="11" t="inlineStr">
+      <c r="BD46" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE47" s="11"/>
-      <c r="BF47" s="11" t="inlineStr">
+      <c r="BE46" s="11"/>
+      <c r="BF46" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG47" s="11"/>
-      <c r="BH47" s="12"/>
-      <c r="BI47" s="20"/>
-      <c r="BJ47" s="20" t="inlineStr">
+      <c r="BG46" s="11"/>
+      <c r="BH46" s="12"/>
+      <c r="BI46" s="20"/>
+      <c r="BJ46" s="20" t="inlineStr">
         <is>
           <t>2.15 千克</t>
         </is>
       </c>
-      <c r="BK47" s="20"/>
-      <c r="BL47" s="20" t="inlineStr">
+      <c r="BK46" s="20"/>
+      <c r="BL46" s="20" t="inlineStr">
         <is>
           <t>28長さ x 28幅 x 9.4高さ cm</t>
         </is>
       </c>
-      <c r="BM47" s="20"/>
-      <c r="BN47" s="20" t="inlineStr">
+      <c r="BM46" s="20"/>
+      <c r="BN46" s="20" t="inlineStr">
         <is>
           <t>3.32 kg</t>
         </is>
       </c>
-      <c r="BO47" s="20" t="inlineStr">
+      <c r="BO46" s="20" t="inlineStr">
         <is>
           <t>3.32 kg</t>
         </is>
       </c>
-      <c r="BP47" s="20" t="inlineStr">
+      <c r="BP46" s="20" t="inlineStr">
         <is>
           <t>39.4 x 33.2 x 13.3 cm</t>
         </is>
       </c>
-      <c r="BQ47" s="20" t="inlineStr">
+      <c r="BQ46" s="20" t="inlineStr">
         <is>
           <t>39.40 x 33.20 x 13.30 cm</t>
         </is>
       </c>
-      <c r="BR47" s="11" t="inlineStr">
+      <c r="BR46" s="11" t="inlineStr">
         <is>
           <t>标准</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11">
-        <v>47</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="12" t="inlineStr">
-        <is>
-          <t>B0H3TTLL3S</t>
-        </is>
-      </c>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>roborock</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/stores/Roborock/page/5E4CAAB4-2101-4304-A4F8-E09C730688AE?lp_asin=B0H3TTLL3S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>roborock (套装购买)Qrevo L Pro扫地机器人 &amp; 消耗品垃圾收集用纸袋(3件)套装</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>套装内容:Qrevo L Pro扫地机、垃圾收集用纸袋(3片)
-垃圾收集用纸袋：为了保持垃圾收集性能，请在垃圾收集托盘用的一次性纸袋满了之后立即更换。
-为了确保产品的性能和安全性，建议使用Roborock原装配件。使用非原装配件时，清洁性能可能会降低或造成故障。</t>
-        </is>
-      </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H3TTLL3S?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31vss+ev80L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>B0H3TTLL3S</t>
-        </is>
-      </c>
-      <c r="M48" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
-        </is>
-      </c>
-      <c r="N48" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O48" s="13">
-        <v>21389</v>
-      </c>
-      <c r="P48" s="13">
-        <v>-107630</v>
-      </c>
-      <c r="Q48" s="14">
-        <v>-1.87</v>
-      </c>
-      <c r="R48" s="15" t="inlineStr">
-        <is>
-          <t>机器人 (家居、厨具、家装)</t>
-        </is>
-      </c>
-      <c r="S48" s="16" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="T48" s="13">
-        <v>23</v>
-      </c>
-      <c r="U48" s="14">
-        <v>-0.86</v>
-      </c>
-      <c r="V48" s="13">
-        <v>1426184</v>
-      </c>
-      <c r="W48" s="13"/>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="13">
-        <v>62008</v>
-      </c>
-      <c r="AA48" s="2"/>
-      <c r="AB48" s="1"/>
-      <c r="AC48" s="2"/>
-      <c r="AD48" s="17"/>
-      <c r="AE48" s="13"/>
-      <c r="AF48" s="18"/>
-      <c r="AG48" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="13"/>
-      <c r="AI48" s="14">
-        <v>0.85</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AL48" s="17">
-        <v>116</v>
-      </c>
-      <c r="AM48" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN48" s="11"/>
-      <c r="AO48" s="11"/>
-      <c r="AP48" s="2"/>
-      <c r="AQ48" s="17">
-        <v>5</v>
-      </c>
-      <c r="AR48" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS48" s="12" t="inlineStr">
-        <is>
-          <t>Roborock JP</t>
-        </is>
-      </c>
-      <c r="AT48" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU48" s="11" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV48" s="12" t="inlineStr">
-        <is>
-          <t>KWUN TONG 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW48" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJLV5TPJIYO7G</t>
-        </is>
-      </c>
-      <c r="AX48" s="11"/>
-      <c r="AY48" s="11"/>
-      <c r="AZ48" s="11"/>
-      <c r="BA48" s="11"/>
-      <c r="BB48" s="11"/>
-      <c r="BC48" s="11"/>
-      <c r="BD48" s="11"/>
-      <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
-      <c r="BG48" s="11"/>
-      <c r="BH48" s="12"/>
-      <c r="BI48" s="20"/>
-      <c r="BJ48" s="20"/>
-      <c r="BK48" s="20"/>
-      <c r="BL48" s="20"/>
-      <c r="BM48" s="20"/>
-      <c r="BN48" s="20"/>
-      <c r="BO48" s="20"/>
-      <c r="BP48" s="20"/>
-      <c r="BQ48" s="20"/>
-      <c r="BR48" s="11"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11">
-        <v>48</v>
-      </c>
-      <c r="B49" s="11"/>
-      <c r="C49" s="12" t="inlineStr">
+    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="11">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>B0DWK6R1WY</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>颜色: 2-白色</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E47" s="12" t="inlineStr">
         <is>
           <t>品牌: Mova | 型号名称: P50 Ultra | 推荐表面: 大理石 | 特殊功能: 激光雷达导航, 自动拖把清洗, 虚拟边界, 进阶定制清洁, 防碰撞 | 颜色: 白色</t>
         </is>
       </c>
-      <c r="F49" s="12" t="inlineStr">
+      <c r="F47" s="12" t="inlineStr">
         <is>
           <t>Mova</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="G47" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/-/zh/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DWK6R1WY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
-      <c r="H49" s="12" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Mova P50 Ultra 机器人吸尘器 全自动 可伸缩拖把和刷子 19,000Pa 吸力 75℃温水拖把自动清洗和干燥功能 自动垃圾收集 高精度测绘 清洁路径确认 自动避障 Mova LDS 激光导航 防毛发缠绕 防摔 防碰撞 加压双旋转拖把 高端型 高速充电 2.4GHz Wi-Fi 支持 应用支持 制造商三年保修</t>
         </is>
       </c>
-      <c r="I49" s="12" t="inlineStr">
+      <c r="I47" s="12" t="inlineStr">
         <is>
           <t>【完全自动清洁】MOVA P50 Ultra配备了完全自动功能的清扫功能和拖把功能的组合，实现彻底清洁。 自立型底座站可自动收集最多75天的垃圾，并用75℃的温水自动清洗拖把，保持清洁状态。 此外,45°C的温风,使拖把干燥,清洁更卫生。
 【19,000Pa的强力吸力】拥有最高19,000Pa的强力吸力，可以有效吸入各种大小的灰尘和长毛发等杂物。 从地毯到地板都可以清洁。
@@ -19860,238 +19419,238 @@
 【通过应用程序轻松操作】即使外出时，也可以通过智能手机应用程序进行远程操作。 只需一键即可轻松管理宠物的声音通话、打扫计划的设置、擦拭和吸尘器的次数等。</t>
         </is>
       </c>
-      <c r="J49" s="12" t="inlineStr">
+      <c r="J47" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B0DWK6R1WY?psc=1</t>
         </is>
       </c>
-      <c r="K49" s="12" t="inlineStr">
+      <c r="K47" s="12" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/61NvFPx0eRL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L49" s="12" t="inlineStr">
+      <c r="L47" s="12" t="inlineStr">
         <is>
           <t>B0GX54VDZS</t>
         </is>
       </c>
-      <c r="M49" s="12" t="inlineStr">
+      <c r="M47" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
         </is>
       </c>
-      <c r="N49" s="12" t="inlineStr">
+      <c r="N47" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装</t>
         </is>
       </c>
-      <c r="O49" s="13">
+      <c r="O47" s="13">
         <v>46364</v>
       </c>
-      <c r="P49" s="13">
+      <c r="P47" s="13">
         <v>12959</v>
       </c>
-      <c r="Q49" s="14">
+      <c r="Q47" s="14">
         <v>0.13</v>
       </c>
-      <c r="R49" s="15" t="inlineStr">
+      <c r="R47" s="15" t="inlineStr">
         <is>
           <t>机器人 (家居、厨具、家装)</t>
         </is>
       </c>
-      <c r="S49" s="16" t="inlineStr">
+      <c r="S47" s="16" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="T49" s="13">
+      <c r="T47" s="13">
         <v>14</v>
       </c>
-      <c r="U49" s="14">
+      <c r="U47" s="14">
         <v>-0.72</v>
       </c>
-      <c r="V49" s="13">
+      <c r="V47" s="13">
         <v>768586</v>
       </c>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="17">
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="17">
         <v>1</v>
       </c>
-      <c r="Z49" s="13">
+      <c r="Z47" s="13">
         <v>349</v>
       </c>
-      <c r="AA49" s="2"/>
-      <c r="AB49" s="1"/>
-      <c r="AC49" s="2"/>
-      <c r="AD49" s="17">
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="17">
         <v>1216</v>
       </c>
-      <c r="AE49" s="13">
+      <c r="AE47" s="13">
         <v>0</v>
       </c>
-      <c r="AF49" s="18">
+      <c r="AF47" s="18">
         <v>4.2</v>
       </c>
-      <c r="AG49" s="19">
+      <c r="AG47" s="19">
         <v>0</v>
       </c>
-      <c r="AH49" s="13">
+      <c r="AH47" s="13">
         <v>1532</v>
       </c>
-      <c r="AI49" s="14">
+      <c r="AI47" s="14">
         <v>0.82</v>
       </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="11" t="inlineStr">
+      <c r="AJ47"/>
+      <c r="AK47" s="11" t="inlineStr">
         <is>
           <t>2025-02-28</t>
         </is>
       </c>
-      <c r="AL49" s="17">
+      <c r="AL47" s="17">
         <v>577</v>
       </c>
-      <c r="AM49" s="11" t="inlineStr">
+      <c r="AM47" s="11" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AN49" s="11"/>
-      <c r="AO49" s="11"/>
-      <c r="AP49" s="2"/>
-      <c r="AQ49" s="17">
+      <c r="AN47" s="11"/>
+      <c r="AO47" s="11"/>
+      <c r="AP47" s="2"/>
+      <c r="AQ47" s="17">
         <v>10</v>
       </c>
-      <c r="AR49" s="17">
+      <c r="AR47" s="17">
         <v>1</v>
       </c>
-      <c r="AS49" s="12" t="inlineStr">
+      <c r="AS47" s="12" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="AT49" s="11" t="inlineStr">
+      <c r="AT47" s="11" t="inlineStr">
         <is>
           <t>AMZ</t>
         </is>
       </c>
-      <c r="AU49" s="11" t="inlineStr">
+      <c r="AU47" s="11" t="inlineStr">
         <is>
           <t>CN(HK)</t>
         </is>
       </c>
-      <c r="AV49" s="12" t="inlineStr">
+      <c r="AV47" s="12" t="inlineStr">
         <is>
           <t>HONG KONG 000 HK</t>
         </is>
       </c>
-      <c r="AW49" s="11"/>
-      <c r="AX49" s="11"/>
-      <c r="AY49" s="11"/>
-      <c r="AZ49" s="11"/>
-      <c r="BA49" s="11"/>
-      <c r="BB49" s="11"/>
-      <c r="BC49" s="11" t="inlineStr">
+      <c r="AW47" s="11"/>
+      <c r="AX47" s="11"/>
+      <c r="AY47" s="11"/>
+      <c r="AZ47" s="11"/>
+      <c r="BA47" s="11"/>
+      <c r="BB47" s="11"/>
+      <c r="BC47" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="11" t="inlineStr">
+      <c r="BD47" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE49" s="11"/>
-      <c r="BF49" s="11" t="inlineStr">
+      <c r="BE47" s="11"/>
+      <c r="BF47" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG49" s="11"/>
-      <c r="BH49" s="12" t="inlineStr">
+      <c r="BG47" s="11"/>
+      <c r="BH47" s="12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20" t="inlineStr">
+      <c r="BI47" s="20"/>
+      <c r="BJ47" s="20" t="inlineStr">
         <is>
           <t>13.13 千克</t>
         </is>
       </c>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20" t="inlineStr">
+      <c r="BK47" s="20"/>
+      <c r="BL47" s="20" t="inlineStr">
         <is>
           <t>30 x 30 x 40 cm</t>
         </is>
       </c>
-      <c r="BM49" s="20" t="inlineStr">
+      <c r="BM47" s="20" t="inlineStr">
         <is>
           <t>30.00 x 30.00 x 40.00 cm</t>
         </is>
       </c>
-      <c r="BN49" s="20" t="inlineStr">
+      <c r="BN47" s="20" t="inlineStr">
         <is>
           <t>20.56 kg</t>
         </is>
       </c>
-      <c r="BO49" s="20" t="inlineStr">
+      <c r="BO47" s="20" t="inlineStr">
         <is>
           <t>20.56 kg</t>
         </is>
       </c>
-      <c r="BP49" s="20" t="inlineStr">
+      <c r="BP47" s="20" t="inlineStr">
         <is>
           <t>60.5 x 54 x 49.5 cm</t>
         </is>
       </c>
-      <c r="BQ49" s="20" t="inlineStr">
+      <c r="BQ47" s="20" t="inlineStr">
         <is>
           <t>60.50 x 54.00 x 49.50 cm</t>
         </is>
       </c>
-      <c r="BR49" s="11" t="inlineStr">
+      <c r="BR47" s="11" t="inlineStr">
         <is>
           <t>大件</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
+    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="11">
+        <v>47</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>B0876QMDVC</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>尺寸: Extra Large</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr">
         <is>
           <t>品牌: CAR-BOY | 材质: EVA树脂、丙烯酸类粘着剂 | 颜色: 木纹标签 | 商品重量: 545 克 | 商品尺寸: 90长度 x 15.3宽度 x 4高度 厘米</t>
         </is>
       </c>
-      <c r="F50" s="12" t="inlineStr">
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>カーボーイ</t>
         </is>
       </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%AB%E3%83%BC%E3%83%9C%E3%83%BC%E3%82%A4/page/63CE72CE-04BB-4920-AF6D-6B64CA525BA1?lp_asin=B0876QMDVC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>不痛快的倾斜坡 (2L)</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>约宽153×长900×高40
 扫地机器人容易乘坐!
@@ -20100,224 +19659,224 @@
 已粘贴专用胶带。</t>
         </is>
       </c>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B0876QMDVC?psc=1</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
+      <c r="K48" s="12" t="inlineStr">
         <is>
           <t>https://m.media-amazon.com/images/I/51cNP2qpwUL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L48" s="12" t="inlineStr">
         <is>
           <t>B0876V7WR1</t>
         </is>
       </c>
-      <c r="M50" s="12" t="inlineStr">
+      <c r="M48" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
         </is>
       </c>
-      <c r="N50" s="12" t="inlineStr">
+      <c r="N48" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装</t>
         </is>
       </c>
-      <c r="O50" s="13">
+      <c r="O48" s="13">
         <v>26417</v>
       </c>
-      <c r="P50" s="13">
+      <c r="P48" s="13">
         <v>1208</v>
       </c>
-      <c r="Q50" s="14">
+      <c r="Q48" s="14">
         <v>0.46</v>
       </c>
-      <c r="R50" s="15" t="inlineStr">
+      <c r="R48" s="15" t="inlineStr">
         <is>
           <t>机器人 (家居、厨具、家装)</t>
         </is>
       </c>
-      <c r="S50" s="16" t="inlineStr">
+      <c r="S48" s="16" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="T50" s="13">
+      <c r="T48" s="13">
         <v>307</v>
       </c>
-      <c r="U50" s="14">
+      <c r="U48" s="14">
         <v>-0.48</v>
       </c>
-      <c r="V50" s="13">
+      <c r="V48" s="13">
         <v>756448</v>
       </c>
-      <c r="W50" s="13" t="inlineStr">
+      <c r="W48" s="13" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="X50" s="13">
+      <c r="X48" s="13">
         <v>123200</v>
       </c>
-      <c r="Y50" s="17">
+      <c r="Y48" s="17">
         <v>4</v>
       </c>
-      <c r="Z50" s="13">
+      <c r="Z48" s="13">
         <v>2464</v>
       </c>
-      <c r="AA50" s="2"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="17">
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="17">
         <v>206</v>
       </c>
-      <c r="AE50" s="13">
+      <c r="AE48" s="13">
         <v>4</v>
       </c>
-      <c r="AF50" s="18">
+      <c r="AF48" s="18">
         <v>4.2</v>
       </c>
-      <c r="AG50" s="19">
+      <c r="AG48" s="19">
         <v>0.013000000000000001</v>
       </c>
-      <c r="AH50" s="13">
+      <c r="AH48" s="13">
         <v>781</v>
       </c>
-      <c r="AI50" s="14">
+      <c r="AI48" s="14">
         <v>0.53</v>
       </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11" t="inlineStr">
+      <c r="AJ48"/>
+      <c r="AK48" s="11" t="inlineStr">
         <is>
           <t>2020-06-06</t>
         </is>
       </c>
-      <c r="AL50" s="17">
+      <c r="AL48" s="17">
         <v>2305</v>
       </c>
-      <c r="AM50" s="11" t="inlineStr">
+      <c r="AM48" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN50" s="11"/>
-      <c r="AO50" s="11"/>
-      <c r="AP50" s="2"/>
-      <c r="AQ50" s="17">
+      <c r="AN48" s="11"/>
+      <c r="AO48" s="11"/>
+      <c r="AP48" s="2"/>
+      <c r="AQ48" s="17">
         <v>8</v>
       </c>
-      <c r="AR50" s="17">
+      <c r="AR48" s="17">
         <v>11</v>
       </c>
-      <c r="AS50" s="12" t="inlineStr">
+      <c r="AS48" s="12" t="inlineStr">
         <is>
           <t>Amazon</t>
         </is>
       </c>
-      <c r="AT50" s="11" t="inlineStr">
+      <c r="AT48" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11" t="inlineStr">
+      <c r="AU48" s="11"/>
+      <c r="AV48" s="12"/>
+      <c r="AW48" s="11"/>
+      <c r="AX48" s="11"/>
+      <c r="AY48" s="11"/>
+      <c r="AZ48" s="11"/>
+      <c r="BA48" s="11"/>
+      <c r="BB48" s="11"/>
+      <c r="BC48" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD50" s="11" t="inlineStr">
+      <c r="BD48" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11" t="inlineStr">
+      <c r="BE48" s="11"/>
+      <c r="BF48" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20" t="inlineStr">
+      <c r="BG48" s="11"/>
+      <c r="BH48" s="12"/>
+      <c r="BI48" s="20"/>
+      <c r="BJ48" s="20" t="inlineStr">
         <is>
           <t>545 克</t>
         </is>
       </c>
-      <c r="BK50" s="20"/>
-      <c r="BL50" s="20" t="inlineStr">
+      <c r="BK48" s="20"/>
+      <c r="BL48" s="20" t="inlineStr">
         <is>
           <t>90長さ x 15.3幅 x 4高さ cm</t>
         </is>
       </c>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20" t="inlineStr">
+      <c r="BM48" s="20"/>
+      <c r="BN48" s="20" t="inlineStr">
         <is>
           <t>600 g</t>
         </is>
       </c>
-      <c r="BO50" s="20" t="inlineStr">
+      <c r="BO48" s="20" t="inlineStr">
         <is>
           <t>600.00 g</t>
         </is>
       </c>
-      <c r="BP50" s="20" t="inlineStr">
+      <c r="BP48" s="20" t="inlineStr">
         <is>
           <t>95 x 16.7 x 4 cm</t>
         </is>
       </c>
-      <c r="BQ50" s="20" t="inlineStr">
+      <c r="BQ48" s="20" t="inlineStr">
         <is>
           <t>95.00 x 16.70 x 4.00 cm</t>
         </is>
       </c>
-      <c r="BR50" s="11" t="inlineStr">
+      <c r="BR48" s="11" t="inlineStr">
         <is>
           <t>大件</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
+    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="11">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>B0D631PKXX</t>
         </is>
       </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="D49" s="12"/>
+      <c r="E49" s="12" t="inlineStr">
         <is>
           <t>品牌: 生活電彩 | 型号名称: 扫除机器人 | 推荐表面: 地板 | 特殊功能: 宠物毛发清扫, 轻巧, 防跌落 | 颜色: 白色</t>
         </is>
       </c>
-      <c r="F51" s="12" t="inlineStr">
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>生活電彩</t>
         </is>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E7%94%9F%E6%B4%BB%E9%9B%BB%E5%BD%A9</t>
         </is>
       </c>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>生活电彩 扫地机器人 扫地机器人 全自动吸尘器 薄型 宠物毛 USB充电 防止掉落 国内制造商</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I49" s="12" t="inlineStr">
         <is>
           <t>生活電彩株式会社是一家日本家电制造商，专注于提供必要且足够功能的产品，并在大型家电零售店等渠道以合理的价格推出令人满意的商品。保修期：从购买日起一年内享受制造商保修。如果出现故障，请遵照随附的日语使用说明书（带保修书）联系制造商。我们提供100%的日本国内支持。
 尺寸:25.4厘米×25厘米×高度7.6厘米。重量:1.2千克。集尘容量:约150毫升。由于占据了典型扫地机器人面积的约70%，即使在其他扫地机器人无法进入的狭小空间，也能进行清扫。
@@ -20328,189 +19887,189 @@
 【注意事项】在颜色较深、反射较弱的地毯等清扫表面上，传感器可能会误动作，导致机器不断后退或停止，或者无法正常运行。</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J49" s="12" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/dp/B0D631PKXX?psc=1</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
+      <c r="K49" s="12" t="inlineStr">
         <is>
           <t>https://images-na.ssl-images-amazon.com/images/I/61hHXam6nxL._AC_US600_.jpg</t>
         </is>
       </c>
-      <c r="L51" s="12" t="inlineStr">
+      <c r="L49" s="12" t="inlineStr">
         <is>
           <t>B0D631PKXX</t>
         </is>
       </c>
-      <c r="M51" s="12" t="inlineStr">
+      <c r="M49" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装:消费性电子产品:电器:吸尘器:机器人</t>
         </is>
       </c>
-      <c r="N51" s="12" t="inlineStr">
+      <c r="N49" s="12" t="inlineStr">
         <is>
           <t>家居、厨具、家装</t>
         </is>
       </c>
-      <c r="O51" s="13">
+      <c r="O49" s="13">
         <v>48848</v>
       </c>
-      <c r="P51" s="13">
+      <c r="P49" s="13">
         <v>-80217</v>
       </c>
-      <c r="Q51" s="14">
+      <c r="Q49" s="14">
         <v>-0.44</v>
       </c>
-      <c r="R51" s="15" t="inlineStr">
+      <c r="R49" s="15" t="inlineStr">
         <is>
           <t>机器人 (家居、厨具、家装)</t>
         </is>
       </c>
-      <c r="S51" s="16" t="inlineStr">
+      <c r="S49" s="16" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="T51" s="13">
+      <c r="T49" s="13">
         <v>13</v>
       </c>
-      <c r="U51" s="14">
+      <c r="U49" s="14">
         <v>1.88</v>
       </c>
-      <c r="V51" s="13">
+      <c r="V49" s="13">
         <v>121017</v>
       </c>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17">
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="17">
         <v>1</v>
       </c>
-      <c r="Z51" s="13">
+      <c r="Z49" s="13">
         <v>9216</v>
       </c>
-      <c r="AA51" s="2"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="17">
+      <c r="AA49" s="2"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="17">
         <v>7</v>
       </c>
-      <c r="AE51" s="13">
+      <c r="AE49" s="13">
         <v>0</v>
       </c>
-      <c r="AF51" s="18">
+      <c r="AF49" s="18">
         <v>3.6</v>
       </c>
-      <c r="AG51" s="19">
+      <c r="AG49" s="19">
         <v>0</v>
       </c>
-      <c r="AH51" s="13">
+      <c r="AH49" s="13">
         <v>472</v>
       </c>
-      <c r="AI51" s="14">
+      <c r="AI49" s="14">
         <v>0.8</v>
       </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11" t="inlineStr">
+      <c r="AJ49"/>
+      <c r="AK49" s="11" t="inlineStr">
         <is>
           <t>2024-06-04</t>
         </is>
       </c>
-      <c r="AL51" s="17">
+      <c r="AL49" s="17">
         <v>845</v>
       </c>
-      <c r="AM51" s="11" t="inlineStr">
+      <c r="AM49" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51" s="2"/>
-      <c r="AQ51" s="17">
+      <c r="AN49" s="11"/>
+      <c r="AO49" s="11"/>
+      <c r="AP49" s="2"/>
+      <c r="AQ49" s="17">
         <v>9</v>
       </c>
-      <c r="AR51" s="17">
+      <c r="AR49" s="17">
         <v>3</v>
       </c>
-      <c r="AS51" s="12" t="inlineStr">
+      <c r="AS49" s="12" t="inlineStr">
         <is>
           <t>シップスコアーズ株式会社 物販事業部</t>
         </is>
       </c>
-      <c r="AT51" s="11" t="inlineStr">
+      <c r="AT49" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU51" s="11" t="inlineStr">
+      <c r="AU49" s="11" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="AV51" s="12" t="inlineStr">
+      <c r="AV49" s="12" t="inlineStr">
         <is>
           <t>中央区 東京都 1030026 JP</t>
         </is>
       </c>
-      <c r="AW51" s="11" t="inlineStr">
+      <c r="AW49" s="11" t="inlineStr">
         <is>
           <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JV3X47LB9U8C</t>
         </is>
       </c>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11" t="inlineStr">
+      <c r="AX49" s="11"/>
+      <c r="AY49" s="11"/>
+      <c r="AZ49" s="11"/>
+      <c r="BA49" s="11"/>
+      <c r="BB49" s="11"/>
+      <c r="BC49" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD51" s="11" t="inlineStr">
+      <c r="BD49" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20" t="inlineStr">
+      <c r="BE49" s="11"/>
+      <c r="BF49" s="11"/>
+      <c r="BG49" s="11"/>
+      <c r="BH49" s="12"/>
+      <c r="BI49" s="20"/>
+      <c r="BJ49" s="20" t="inlineStr">
         <is>
           <t>1.2 千克</t>
         </is>
       </c>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20" t="inlineStr">
+      <c r="BK49" s="20"/>
+      <c r="BL49" s="20" t="inlineStr">
         <is>
           <t>25.3長さ x 25幅 x 7.6高さ cm</t>
         </is>
       </c>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20" t="inlineStr">
+      <c r="BM49" s="20"/>
+      <c r="BN49" s="20" t="inlineStr">
         <is>
           <t>1.64 kg</t>
         </is>
       </c>
-      <c r="BO51" s="20" t="inlineStr">
+      <c r="BO49" s="20" t="inlineStr">
         <is>
           <t>1.64 kg</t>
         </is>
       </c>
-      <c r="BP51" s="20" t="inlineStr">
+      <c r="BP49" s="20" t="inlineStr">
         <is>
           <t>31.4 x 31.2 x 10.7 cm</t>
         </is>
       </c>
-      <c r="BQ51" s="20" t="inlineStr">
+      <c r="BQ49" s="20" t="inlineStr">
         <is>
           <t>31.40 x 31.20 x 10.70 cm</t>
         </is>
       </c>
-      <c r="BR51" s="11" t="inlineStr">
+      <c r="BR49" s="11" t="inlineStr">
         <is>
           <t>标准</t>
         </is>
@@ -20849,70 +20408,54 @@
     <hyperlink ref="M43" r:id="rId327" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
     <hyperlink ref="N43" r:id="rId328"/>
     <hyperlink ref="AW43" r:id="rId329" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MXWPZJBJOY5S"/>
-    <hyperlink ref="C44" r:id="rId330" tooltip="https://www.amazon.co.jp/dp/B0H3SZKNG5"/>
-    <hyperlink ref="G44" r:id="rId331" tooltip="https://www.amazon.co.jp/stores/Roborock/page/5E4CAAB4-2101-4304-A4F8-E09C730688AE?lp_asin=B0H3SZKNG5&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J44" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0H3SZKNG5?psc=1"/>
-    <hyperlink ref="K44" r:id="rId333" tooltip="https://m.media-amazon.com/images/I/310n8Y3Io5L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0H3SZKNG5"/>
+    <hyperlink ref="C44" r:id="rId330" tooltip="https://www.amazon.co.jp/dp/B0FD3Q3HDQ"/>
+    <hyperlink ref="G44" r:id="rId331" tooltip="https://www.amazon.co.jp/-/zh/stores/Lefant/page/9C72F38B-D744-433C-984D-924C2CF60DBF?lp_asin=B0FD3Q3HDQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J44" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0FD3Q3HDQ?psc=1"/>
+    <hyperlink ref="K44" r:id="rId333" tooltip="https://m.media-amazon.com/images/I/41a1mhAFYmL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0H94R793P"/>
     <hyperlink ref="M44" r:id="rId335" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
     <hyperlink ref="N44" r:id="rId336"/>
-    <hyperlink ref="AW44" r:id="rId337" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJLV5TPJIYO7G"/>
-    <hyperlink ref="C45" r:id="rId338" tooltip="https://www.amazon.co.jp/dp/B0FD3Q3HDQ"/>
-    <hyperlink ref="G45" r:id="rId339" tooltip="https://www.amazon.co.jp/-/zh/stores/Lefant/page/9C72F38B-D744-433C-984D-924C2CF60DBF?lp_asin=B0FD3Q3HDQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0FD3Q3HDQ?psc=1"/>
-    <hyperlink ref="K45" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/41a1mhAFYmL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0H94R793P"/>
+    <hyperlink ref="AW44" r:id="rId337" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MNLSSQJOAPSN"/>
+    <hyperlink ref="C45" r:id="rId338" tooltip="https://www.amazon.co.jp/dp/B0FSKG1CGR"/>
+    <hyperlink ref="G45" r:id="rId339" tooltip="https://www.amazon.co.jp/-/zh/stores/HOBOT/page/5FD3BD3C-4B59-4EF0-998B-639025A0DFC5?lp_asin=B0FSKG1CGR&amp;ref_=ast_bln"/>
+    <hyperlink ref="J45" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0FSKG1CGR?psc=1"/>
+    <hyperlink ref="K45" r:id="rId341" tooltip="https://m.media-amazon.com/images/I/319+CshNDML._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0FSKG1CGR"/>
     <hyperlink ref="M45" r:id="rId343" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
     <hyperlink ref="N45" r:id="rId344"/>
-    <hyperlink ref="AW45" r:id="rId345" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1MNLSSQJOAPSN"/>
-    <hyperlink ref="C46" r:id="rId346" tooltip="https://www.amazon.co.jp/dp/B0FSKG1CGR"/>
-    <hyperlink ref="G46" r:id="rId347" tooltip="https://www.amazon.co.jp/-/zh/stores/HOBOT/page/5FD3BD3C-4B59-4EF0-998B-639025A0DFC5?lp_asin=B0FSKG1CGR&amp;ref_=ast_bln"/>
-    <hyperlink ref="J46" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0FSKG1CGR?psc=1"/>
-    <hyperlink ref="K46" r:id="rId349" tooltip="https://m.media-amazon.com/images/I/319+CshNDML._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B0FSKG1CGR"/>
+    <hyperlink ref="AW45" r:id="rId345" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHEZ9DMV8Q508"/>
+    <hyperlink ref="C46" r:id="rId346" tooltip="https://www.amazon.co.jp/dp/B0F4CKCQSR"/>
+    <hyperlink ref="G46" r:id="rId347" tooltip="https://www.amazon.co.jp/-/zh/stores/OKPLIFE/page/23AA7D3D-6376-403F-8AD6-A176BA24E310?lp_asin=B0F4CKCQSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J46" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0F4CKCQSR?psc=1"/>
+    <hyperlink ref="K46" r:id="rId349" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NLEOxrsQL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B0GDFJ5R1P"/>
     <hyperlink ref="M46" r:id="rId351" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
     <hyperlink ref="N46" r:id="rId352"/>
-    <hyperlink ref="AW46" r:id="rId353" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AHEZ9DMV8Q508"/>
-    <hyperlink ref="C47" r:id="rId354" tooltip="https://www.amazon.co.jp/dp/B0F4CKCQSR"/>
-    <hyperlink ref="G47" r:id="rId355" tooltip="https://www.amazon.co.jp/-/zh/stores/OKPLIFE/page/23AA7D3D-6376-403F-8AD6-A176BA24E310?lp_asin=B0F4CKCQSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0F4CKCQSR?psc=1"/>
-    <hyperlink ref="K47" r:id="rId357" tooltip="https://images-na.ssl-images-amazon.com/images/I/71NLEOxrsQL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B0GDFJ5R1P"/>
+    <hyperlink ref="AW46" r:id="rId353" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A95AMKZGJE5P0"/>
+    <hyperlink ref="C47" r:id="rId354" tooltip="https://www.amazon.co.jp/dp/B0DWK6R1WY"/>
+    <hyperlink ref="G47" r:id="rId355" tooltip="https://www.amazon.co.jp/-/zh/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DWK6R1WY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0DWK6R1WY?psc=1"/>
+    <hyperlink ref="K47" r:id="rId357" tooltip="https://images-na.ssl-images-amazon.com/images/I/61NvFPx0eRL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B0GX54VDZS"/>
     <hyperlink ref="M47" r:id="rId359" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
     <hyperlink ref="N47" r:id="rId360"/>
-    <hyperlink ref="AW47" r:id="rId361" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A95AMKZGJE5P0"/>
-    <hyperlink ref="C48" r:id="rId362" tooltip="https://www.amazon.co.jp/dp/B0H3TTLL3S"/>
-    <hyperlink ref="G48" r:id="rId363" tooltip="https://www.amazon.co.jp/stores/Roborock/page/5E4CAAB4-2101-4304-A4F8-E09C730688AE?lp_asin=B0H3TTLL3S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J48" r:id="rId364" tooltip="https://www.amazon.co.jp/dp/B0H3TTLL3S?psc=1"/>
-    <hyperlink ref="K48" r:id="rId365" tooltip="https://m.media-amazon.com/images/I/31vss+ev80L._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId366" tooltip="https://www.amazon.co.jp/dp/B0H3TTLL3S"/>
-    <hyperlink ref="M48" r:id="rId367" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
-    <hyperlink ref="N48" r:id="rId368"/>
-    <hyperlink ref="AW48" r:id="rId369" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJLV5TPJIYO7G"/>
-    <hyperlink ref="C49" r:id="rId370" tooltip="https://www.amazon.co.jp/dp/B0DWK6R1WY"/>
-    <hyperlink ref="G49" r:id="rId371" tooltip="https://www.amazon.co.jp/-/zh/stores/MOVA/page/1C66BA39-85DA-4EF9-BEE1-43A9D48A27F4?lp_asin=B0DWK6R1WY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0DWK6R1WY?psc=1"/>
-    <hyperlink ref="K49" r:id="rId373" tooltip="https://images-na.ssl-images-amazon.com/images/I/61NvFPx0eRL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B0GX54VDZS"/>
-    <hyperlink ref="M49" r:id="rId375" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
-    <hyperlink ref="N49" r:id="rId376"/>
-    <hyperlink ref="C50" r:id="rId377" tooltip="https://www.amazon.co.jp/dp/B0876QMDVC"/>
-    <hyperlink ref="G50" r:id="rId378" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%AB%E3%83%BC%E3%83%9C%E3%83%BC%E3%82%A4/page/63CE72CE-04BB-4920-AF6D-6B64CA525BA1?lp_asin=B0876QMDVC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId379" tooltip="https://www.amazon.co.jp/dp/B0876QMDVC?psc=1"/>
-    <hyperlink ref="K50" r:id="rId380" tooltip="https://m.media-amazon.com/images/I/51cNP2qpwUL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId381" tooltip="https://www.amazon.co.jp/dp/B0876V7WR1"/>
-    <hyperlink ref="M50" r:id="rId382" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
-    <hyperlink ref="N50" r:id="rId383"/>
-    <hyperlink ref="C51" r:id="rId384" tooltip="https://www.amazon.co.jp/dp/B0D631PKXX"/>
-    <hyperlink ref="G51" r:id="rId385" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E7%94%9F%E6%B4%BB%E9%9B%BB%E5%BD%A9"/>
-    <hyperlink ref="J51" r:id="rId386" tooltip="https://www.amazon.co.jp/dp/B0D631PKXX?psc=1"/>
-    <hyperlink ref="K51" r:id="rId387" tooltip="https://images-na.ssl-images-amazon.com/images/I/61hHXam6nxL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId388" tooltip="https://www.amazon.co.jp/dp/B0D631PKXX"/>
-    <hyperlink ref="M51" r:id="rId389" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
-    <hyperlink ref="N51" r:id="rId390"/>
-    <hyperlink ref="AW51" r:id="rId391" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JV3X47LB9U8C"/>
+    <hyperlink ref="C48" r:id="rId361" tooltip="https://www.amazon.co.jp/dp/B0876QMDVC"/>
+    <hyperlink ref="G48" r:id="rId362" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%AB%E3%83%BC%E3%83%9C%E3%83%BC%E3%82%A4/page/63CE72CE-04BB-4920-AF6D-6B64CA525BA1?lp_asin=B0876QMDVC&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId363" tooltip="https://www.amazon.co.jp/dp/B0876QMDVC?psc=1"/>
+    <hyperlink ref="K48" r:id="rId364" tooltip="https://m.media-amazon.com/images/I/51cNP2qpwUL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId365" tooltip="https://www.amazon.co.jp/dp/B0876V7WR1"/>
+    <hyperlink ref="M48" r:id="rId366" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
+    <hyperlink ref="N48" r:id="rId367"/>
+    <hyperlink ref="C49" r:id="rId368" tooltip="https://www.amazon.co.jp/dp/B0D631PKXX"/>
+    <hyperlink ref="G49" r:id="rId369" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=%E7%94%9F%E6%B4%BB%E9%9B%BB%E5%BD%A9"/>
+    <hyperlink ref="J49" r:id="rId370" tooltip="https://www.amazon.co.jp/dp/B0D631PKXX?psc=1"/>
+    <hyperlink ref="K49" r:id="rId371" tooltip="https://images-na.ssl-images-amazon.com/images/I/61hHXam6nxL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0D631PKXX"/>
+    <hyperlink ref="M49" r:id="rId373" tooltip="https://www.amazon.co.jp/b?node=2353758051"/>
+    <hyperlink ref="N49" r:id="rId374"/>
+    <hyperlink ref="AW49" r:id="rId375" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JV3X47LB9U8C"/>
   </hyperlinks>
-  <drawing r:id="rId392"/>
+  <drawing r:id="rId376"/>
 </worksheet>
 </file>
 
@@ -20982,7 +20525,7 @@
         <v>82779.50604308986</v>
       </c>
       <c r="G2" s="19">
-        <v>0.295298194796462</v>
+        <v>0.29601783677278853</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21003,7 +20546,7 @@
         <v>68546.69213313161</v>
       </c>
       <c r="G3" s="19">
-        <v>0.20514146795634408</v>
+        <v>0.2056413979052162</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21013,18 +20556,18 @@
         </is>
       </c>
       <c r="B4" s="13">
-        <v>2229</v>
+        <v>2182</v>
       </c>
       <c r="C4" s="13">
-        <v>189180004</v>
+        <v>185476652</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13">
-        <v>84872.14176760879</v>
+        <v>85003.04857928507</v>
       </c>
       <c r="G4" s="19">
-        <v>0.1152950912946775</v>
+        <v>0.11313906460645028</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21045,7 +20588,7 @@
         <v>48032.131350681535</v>
       </c>
       <c r="G5" s="19">
-        <v>0.1669683960068277</v>
+        <v>0.1673752981437312</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21066,7 +20609,7 @@
         <v>80213.67924528301</v>
       </c>
       <c r="G6" s="19">
-        <v>0.0438628252211245</v>
+        <v>0.04396971896712641</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21087,7 +20630,7 @@
         <v>54240.53412462908</v>
       </c>
       <c r="G7" s="19">
-        <v>0.03486267004603528</v>
+        <v>0.03494763040547547</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21108,7 +20651,7 @@
         <v>20409.372197309418</v>
       </c>
       <c r="G8" s="19">
-        <v>0.046138726529767755</v>
+        <v>0.046251166649382974</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21129,7 +20672,7 @@
         <v>19030.476578411406</v>
       </c>
       <c r="G9" s="19">
-        <v>0.025396989603269023</v>
+        <v>0.025458882090635696</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21150,7 +20693,7 @@
         <v>20070.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.019396886153209537</v>
+        <v>0.0194441563828684</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21171,7 +20714,7 @@
         <v>40779.873417721516</v>
       </c>
       <c r="G11" s="19">
-        <v>0.008172554699218952</v>
+        <v>0.008192471222648554</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21192,7 +20735,7 @@
         <v>40065.163398692814</v>
       </c>
       <c r="G12" s="19">
-        <v>0.007913929550509492</v>
+        <v>0.007933215804210308</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21213,7 +20756,7 @@
         <v>42000.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.007293229193606786</v>
+        <v>0.007311002799958519</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21234,7 +20777,7 @@
         <v>64447.0</v>
       </c>
       <c r="G14" s="19">
-        <v>0.0033621269332229867</v>
+        <v>0.0033703204396971897</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21255,7 +20798,7 @@
         <v>22980.0</v>
       </c>
       <c r="G15" s="19">
-        <v>0.003620752081932447</v>
+        <v>0.003629575858135435</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21276,7 +20819,7 @@
         <v>54899.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.0007241504163864894</v>
+        <v>0.000725915171627087</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21297,7 +20840,7 @@
         <v>2464.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.015879584130760876</v>
+        <v>0.015918282692108265</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21318,7 +20861,7 @@
         <v>9309.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.0006724253866445973</v>
+        <v>0.0006740640879394379</v>
       </c>
     </row>
   </sheetData>
@@ -21393,7 +20936,7 @@
         <v>82779.50604308986</v>
       </c>
       <c r="G2" s="19">
-        <v>0.295298194796462</v>
+        <v>0.29601783677278853</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21414,7 +20957,7 @@
         <v>52711.79423613263</v>
       </c>
       <c r="G3" s="19">
-        <v>0.16691667097708582</v>
+        <v>0.16732344706004357</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21435,7 +20978,7 @@
         <v>48032.131350681535</v>
       </c>
       <c r="G4" s="19">
-        <v>0.1669683960068277</v>
+        <v>0.1673752981437312</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21445,18 +20988,18 @@
         </is>
       </c>
       <c r="B5" s="13">
-        <v>1517</v>
+        <v>1470</v>
       </c>
       <c r="C5" s="13">
-        <v>110978444</v>
+        <v>107275092</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13">
-        <v>73156.52208305866</v>
+        <v>72976.25306122449</v>
       </c>
       <c r="G5" s="19">
-        <v>0.07846687011845031</v>
+        <v>0.07622109302084414</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21477,7 +21020,7 @@
         <v>109833.65168539326</v>
       </c>
       <c r="G6" s="19">
-        <v>0.03682822117622717</v>
+        <v>0.03691797158560614</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21498,7 +21041,7 @@
         <v>89906.08424336974</v>
       </c>
       <c r="G7" s="19">
-        <v>0.033155744064552836</v>
+        <v>0.033236544643783054</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21519,7 +21062,7 @@
         <v>89800.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.028448766358040656</v>
+        <v>0.02851809602820699</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21540,7 +21083,7 @@
         <v>80000.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.030621217607200123</v>
+        <v>0.03069584154308825</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21561,7 +21104,7 @@
         <v>72545.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.03175916826152175</v>
+        <v>0.03183656538421653</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21582,7 +21125,7 @@
         <v>20409.372197309418</v>
       </c>
       <c r="G11" s="19">
-        <v>0.046138726529767755</v>
+        <v>0.046251166649382974</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21603,7 +21146,7 @@
         <v>50200.0</v>
       </c>
       <c r="G12" s="19">
-        <v>0.010707081156571666</v>
+        <v>0.010733174323343357</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21624,7 +21167,7 @@
         <v>20070.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.019396886153209537</v>
+        <v>0.0194441563828684</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21645,7 +21188,7 @@
         <v>18740.944444444445</v>
       </c>
       <c r="G14" s="19">
-        <v>0.019552061242435213</v>
+        <v>0.01959970963393135</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21666,7 +21209,7 @@
         <v>40779.873417721516</v>
       </c>
       <c r="G15" s="19">
-        <v>0.008172554699218952</v>
+        <v>0.008192471222648554</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21687,7 +21230,7 @@
         <v>40065.163398692814</v>
       </c>
       <c r="G16" s="19">
-        <v>0.007913929550509492</v>
+        <v>0.007933215804210308</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21708,7 +21251,7 @@
         <v>42000.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.007293229193606786</v>
+        <v>0.007311002799958519</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21729,7 +21272,7 @@
         <v>63600.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.0022241762789013604</v>
+        <v>0.00222959659856891</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21750,7 +21293,7 @@
         <v>19999.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.005844928360833807</v>
+        <v>0.0058591724567043455</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21771,7 +21314,7 @@
         <v>22980.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.003620752081932447</v>
+        <v>0.003629575858135435</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21792,7 +21335,7 @@
         <v>9309.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.0006724253866445973</v>
+        <v>0.0006740640879394379</v>
       </c>
     </row>
   </sheetData>
